--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc55da2da06304c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R147248b31cca42f7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R147248b31cca42f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R59f7d9d3084646c6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R59f7d9d3084646c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R32bb734b18d7463f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R32bb734b18d7463f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R46d90236acd8409a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R46d90236acd8409a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6bb0efc99a624b92"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6bb0efc99a624b92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd3fffd5a6b244e95"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd3fffd5a6b244e95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8e8a738fbd844763"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8e8a738fbd844763"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6b95165036644b98"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6b95165036644b98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3e57fbf6b9ee44af"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3e57fbf6b9ee44af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R35e8664783db4820"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R35e8664783db4820"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R60e2abd63cef4e88"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R60e2abd63cef4e88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc5e4bfefc83f4c90"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc5e4bfefc83f4c90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R798bfeb966d74770"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R798bfeb966d74770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R55cd55421c28454a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/CellLocking/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R55cd55421c28454a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2f3a88b6d2a3493a"/>
   </x:sheets>
 </x:workbook>
 </file>
